--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_155_R16.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_155_R16.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>N. MILUTINOV</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,40 +565,40 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0646</v>
+        <v>2.9593</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5862</v>
+        <v>5.8579</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5216</v>
+        <v>-2.8986</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.6133</v>
+        <v>2.7679</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3206</v>
+        <v>3.2196</v>
       </c>
       <c r="I2" t="n">
-        <v>-1.9338</v>
+        <v>-0.4517</v>
       </c>
       <c r="J2" t="n">
-        <v>0.96</v>
+        <v>6.0449</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6288</v>
+        <v>3.4954</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3312</v>
+        <v>2.5495</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.5733</v>
+        <v>-3.277</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3082</v>
+        <v>-0.2759</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.2651</v>
+        <v>-3.0012</v>
       </c>
       <c r="P2" t="n">
         <v>1.3917</v>
@@ -610,28 +610,28 @@
         <v>2.5515</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3221</v>
+        <v>-1.0585</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8219</v>
+        <v>0.4367</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.4998</v>
+        <v>-1.4952</v>
       </c>
       <c r="V2" t="n">
-        <v>2.9641</v>
+        <v>-0.1418</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9641</v>
+        <v>0.5361</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>N. MILUTINOV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1029</v>
+        <v>2.831</v>
       </c>
       <c r="E3" t="n">
-        <v>5.2367</v>
+        <v>4.4198</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.1339</v>
+        <v>-1.5888</v>
       </c>
       <c r="G3" t="n">
-        <v>2.7679</v>
+        <v>-1.6133</v>
       </c>
       <c r="H3" t="n">
-        <v>3.2196</v>
+        <v>0.3206</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.4517</v>
+        <v>-1.9338</v>
       </c>
       <c r="J3" t="n">
-        <v>6.0449</v>
+        <v>0.96</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4954</v>
+        <v>0.6288</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5495</v>
+        <v>0.3312</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.277</v>
+        <v>-2.5733</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2759</v>
+        <v>-0.3082</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.0012</v>
+        <v>-2.2651</v>
       </c>
       <c r="P3" t="n">
         <v>1.3917</v>
@@ -688,22 +688,22 @@
         <v>2.5515</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.9149</v>
+        <v>0.0885</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1845</v>
+        <v>1.6555</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.7304</v>
+        <v>-1.567</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1418</v>
+        <v>2.9641</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5361</v>
+        <v>2.9641</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4079</v>
+        <v>1.2399</v>
       </c>
       <c r="E4" t="n">
         <v>1.3664</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0416</v>
+        <v>-0.1264</v>
       </c>
       <c r="G4" t="n">
         <v>-0.8431</v>
@@ -766,13 +766,13 @@
         <v>0.232</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4107</v>
+        <v>0.2427</v>
       </c>
       <c r="T4" t="n">
         <v>-0.0589</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4696</v>
+        <v>0.3016</v>
       </c>
       <c r="V4" t="n">
         <v>1.6083</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3051</v>
+        <v>1.1046</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0088</v>
+        <v>1.9091</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.7037</v>
+        <v>-0.8046</v>
       </c>
       <c r="G5" t="n">
         <v>1.0092</v>
@@ -844,13 +844,13 @@
         <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9361</v>
+        <v>-0.1366</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5149</v>
+        <v>0.3855</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4213</v>
+        <v>-0.5221</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. VEZENKOV</t>
+          <t>T. DORSEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6636</v>
+        <v>-0.3717</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9539</v>
+        <v>1.4433</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6175</v>
+        <v>-1.8149</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.6869</v>
+        <v>0.896</v>
       </c>
       <c r="H6" t="n">
-        <v>1.475</v>
+        <v>1.5619</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.162</v>
+        <v>-0.6659</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5938</v>
+        <v>2.2291</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6475</v>
+        <v>1.6805</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0538</v>
+        <v>0.5486</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.2807</v>
+        <v>-1.333</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1725</v>
+        <v>-0.1186</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.1082</v>
+        <v>-1.2144</v>
       </c>
       <c r="P6" t="n">
+        <v>-0.6959</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="R6" t="n">
         <v>0.4639</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-2.3195</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.7834</v>
-      </c>
       <c r="S6" t="n">
-        <v>0.2759</v>
+        <v>-0.7136</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3961</v>
+        <v>0.2322</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.1202</v>
+        <v>-0.9458</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2836</v>
+        <v>0.1418</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2836</v>
+        <v>0.1418</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T. DORSEY</t>
+          <t>S. LEE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9689</v>
+        <v>-0.9625</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7788</v>
+        <v>-0.0634</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7477</v>
+        <v>-0.8992</v>
       </c>
       <c r="G7" t="n">
-        <v>0.896</v>
+        <v>0.4046</v>
       </c>
       <c r="H7" t="n">
-        <v>1.5619</v>
+        <v>-0.3516</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6659</v>
+        <v>0.7562</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2291</v>
+        <v>1.1946</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6805</v>
+        <v>0.0168</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5486</v>
+        <v>1.1778</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.333</v>
+        <v>-0.79</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1186</v>
+        <v>-0.3684</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2144</v>
+        <v>-0.4216</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6959</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.3109</v>
+        <v>-0.4393</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4323</v>
+        <v>-0.0982</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8786</v>
+        <v>-0.3411</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. LEE</t>
+          <t>S. VEZENKOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1141</v>
+        <v>-1.3386</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1813</v>
+        <v>0.7494</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9328</v>
+        <v>-2.088</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4046</v>
+        <v>-1.6869</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3516</v>
+        <v>1.475</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7562</v>
+        <v>-3.162</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1946</v>
+        <v>1.5938</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0168</v>
+        <v>1.6475</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1778</v>
+        <v>-0.0538</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.79</v>
+        <v>-3.2807</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3684</v>
+        <v>-0.1725</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4216</v>
+        <v>-3.1082</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R8" t="n">
-        <v>0.232</v>
+        <v>2.7834</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5909</v>
+        <v>-0.3991</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2161</v>
+        <v>1.1916</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3747</v>
+        <v>-1.5907</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0029</v>
+        <v>-1.743</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2095</v>
+        <v>1.4022</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.2124</v>
+        <v>-3.1452</v>
       </c>
       <c r="G9" t="n">
         <v>0.6328</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4191</v>
+        <v>-0.1592</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1415</v>
+        <v>0.0512</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2776</v>
+        <v>-0.2104</v>
       </c>
       <c r="V9" t="n">
         <v>-2.6805</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1973</v>
+        <v>-3.0378</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2332</v>
+        <v>-1.3761</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9641</v>
+        <v>-1.6617</v>
       </c>
       <c r="G10" t="n">
         <v>-3.7933</v>
@@ -1234,13 +1234,13 @@
         <v>2.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.8859</v>
+        <v>-0.7264</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0395</v>
+        <v>0.8966</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.9254</v>
+        <v>-1.623</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4564</v>
+        <v>-4.4571</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3129</v>
+        <v>-1.5488</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1435</v>
+        <v>-2.9083</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9357</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2166</v>
+        <v>-0.2172</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.3422</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.7947</v>
+        <v>-0.5594</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6083</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5227</v>
+        <v>-3.775899999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>13.4129</v>
+        <v>14.1598</v>
       </c>
       <c r="F12" t="n">
-        <v>-17.9356</v>
+        <v>-17.9357</v>
       </c>
       <c r="G12" t="n">
         <v>-4.161799999999999</v>
@@ -1390,16 +1390,16 @@
         <v>15.077</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.2657</v>
+        <v>-3.5187</v>
       </c>
       <c r="T12" t="n">
-        <v>4.2874</v>
+        <v>5.0344</v>
       </c>
       <c r="U12" t="n">
-        <v>-8.553100000000001</v>
+        <v>-8.553099999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4254000000000004</v>
+        <v>0.4254</v>
       </c>
       <c r="W12" t="n">
         <v>6.2118</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.3775</v>
+        <v>7.1524</v>
       </c>
       <c r="E13" t="n">
-        <v>5.4973</v>
+        <v>6.205</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8802</v>
+        <v>0.9474</v>
       </c>
       <c r="G13" t="n">
         <v>4.4695</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1942</v>
+        <v>0.9691</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9594</v>
+        <v>1.6671</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7653</v>
+        <v>-0.698</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1418</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5974</v>
+        <v>5.4668</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5587</v>
+        <v>3.6767</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0387</v>
+        <v>1.7901</v>
       </c>
       <c r="G14" t="n">
         <v>6.9399</v>
@@ -1546,13 +1546,13 @@
         <v>1.6237</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6286</v>
+        <v>0.2407</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2068</v>
+        <v>-0.4553</v>
       </c>
       <c r="V14" t="n">
         <v>0.1418</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4811</v>
+        <v>4.7842</v>
       </c>
       <c r="E15" t="n">
-        <v>5.0458</v>
+        <v>5.2817</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5647</v>
+        <v>-0.4975</v>
       </c>
       <c r="G15" t="n">
         <v>0.3666</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>0.434</v>
+        <v>0.7371</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7537</v>
+        <v>1.9896</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.3196</v>
+        <v>-1.2524</v>
       </c>
       <c r="V15" t="n">
         <v>3.2166</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6705</v>
+        <v>0.4067</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1336</v>
+        <v>-0.4874</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8041</v>
+        <v>0.8942</v>
       </c>
       <c r="G16" t="n">
         <v>0.8035</v>
@@ -1702,13 +1702,13 @@
         <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>1.4058</v>
+        <v>1.142</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6711</v>
+        <v>1.3172</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2653</v>
+        <v>-0.1753</v>
       </c>
       <c r="V16" t="n">
         <v>-2.0026</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. TAYLOR</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2083</v>
+        <v>0.0409</v>
       </c>
       <c r="E17" t="n">
-        <v>1.398</v>
+        <v>-0.5281</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6063</v>
+        <v>0.569</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7614</v>
+        <v>2.2556</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5606</v>
+        <v>-0.7622</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2009</v>
+        <v>3.0179</v>
       </c>
       <c r="J17" t="n">
-        <v>3.5954</v>
+        <v>1.3875</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1294</v>
+        <v>-0.215</v>
       </c>
       <c r="L17" t="n">
-        <v>2.4659</v>
+        <v>1.6025</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.8339</v>
+        <v>0.8681</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5688</v>
+        <v>-0.5473</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.2651</v>
+        <v>1.4154</v>
       </c>
       <c r="P17" t="n">
         <v>-1.8556</v>
@@ -1780,28 +1780,28 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>0.239</v>
+        <v>1.2492</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1221</v>
+        <v>0.7982</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1169</v>
+        <v>0.4509</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6468</v>
+        <v>-1.6083</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6468</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>N. SAKO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7905</v>
+        <v>-0.2886</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2358</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4454</v>
+        <v>-0.3871</v>
       </c>
       <c r="G18" t="n">
-        <v>2.2556</v>
+        <v>-1.011</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.7622</v>
+        <v>-0.7467</v>
       </c>
       <c r="I18" t="n">
-        <v>3.0179</v>
+        <v>-0.2643</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3875</v>
+        <v>-0.2318</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.215</v>
+        <v>-0.2318</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6025</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8681</v>
+        <v>-0.7792</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5473</v>
+        <v>-0.5149</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4154</v>
+        <v>-0.2643</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4178</v>
+        <v>0.0266</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0905</v>
+        <v>0.3304</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3273</v>
+        <v>-0.3038</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3943</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>K. TAYLOR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8535</v>
+        <v>-0.3313</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1494</v>
+        <v>1.1621</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-1.4934</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7040999999999999</v>
+        <v>0.7614</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3361</v>
+        <v>0.5606</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.368</v>
+        <v>0.2009</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3.5954</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.1294</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.4659</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7040999999999999</v>
+        <v>-2.8339</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3361</v>
+        <v>-0.5688</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.368</v>
+        <v>-2.2651</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1494</v>
+        <v>0.116</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1494</v>
+        <v>-0.1138</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.2298</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.6468</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. SAKO</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8612</v>
+        <v>-0.8535</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3732</v>
+        <v>-0.1494</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.488</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.011</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.7467</v>
+        <v>-0.3361</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2643</v>
+        <v>-0.368</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2318</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2318</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7792</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5149</v>
+        <v>-0.3361</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2643</v>
+        <v>-0.368</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5461</v>
+        <v>-0.1494</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1415</v>
+        <v>-0.1494</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4046</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1451</v>
+        <v>-1.1394</v>
       </c>
       <c r="E21" t="n">
-        <v>4.0312</v>
+        <v>3.9132</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.1763</v>
+        <v>-5.0527</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2103</v>
@@ -2092,13 +2092,13 @@
         <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4863</v>
+        <v>-0.4806</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3462</v>
+        <v>0.2282</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8325</v>
+        <v>-0.7088</v>
       </c>
       <c r="V21" t="n">
         <v>-1.6083</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3201</v>
+        <v>-2.0056</v>
       </c>
       <c r="E22" t="n">
-        <v>3.289</v>
+        <v>2.3454</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.6091</v>
+        <v>-4.351</v>
       </c>
       <c r="G22" t="n">
         <v>-4.7493</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>1.125</v>
+        <v>0.4395</v>
       </c>
       <c r="T22" t="n">
-        <v>1.7695</v>
+        <v>0.8259</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6445</v>
+        <v>-0.3864</v>
       </c>
       <c r="V22" t="n">
         <v>1.6083</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2441</v>
+        <v>-3.305</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6902</v>
+        <v>-0.1354</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9344</v>
+        <v>-3.1696</v>
       </c>
       <c r="G23" t="n">
         <v>-3.7501</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1117</v>
+        <v>1.0508</v>
       </c>
       <c r="T23" t="n">
-        <v>2.0761</v>
+        <v>1.2505</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0356</v>
+        <v>-0.1997</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1418</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1809</v>
+        <v>-3.8321</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6826</v>
+        <v>-3.4467</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4984</v>
+        <v>-0.3855</v>
       </c>
       <c r="G24" t="n">
         <v>-1.0099</v>
@@ -2326,13 +2326,13 @@
         <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1485</v>
+        <v>0.4973</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5228</v>
+        <v>-0.2869</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6713</v>
+        <v>0.7842</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5361</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>4.522800000000001</v>
+        <v>6.095499999999998</v>
       </c>
       <c r="E25" t="n">
-        <v>17.9356</v>
+        <v>17.9357</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.4129</v>
+        <v>-11.8402</v>
       </c>
       <c r="G25" t="n">
         <v>4.161799999999999</v>
@@ -2389,7 +2389,7 @@
         <v>-14.5111</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.155199999999999</v>
+        <v>-8.155200000000001</v>
       </c>
       <c r="O25" t="n">
         <v>-6.356</v>
@@ -2404,13 +2404,13 @@
         <v>11.5979</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2656</v>
+        <v>5.838299999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>8.553000000000001</v>
+        <v>8.553100000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.2875</v>
+        <v>-2.7148</v>
       </c>
       <c r="V25" t="n">
         <v>-0.4254000000000001</v>
